--- a/templates/04_Process_Routing.xlsx
+++ b/templates/04_Process_Routing.xlsx
@@ -425,17 +425,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -494,7 +494,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SKU-A10</t>
+          <t>SKU-E10</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -502,7 +502,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FILL-STD</t>
+          <t>FILL-NEW</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -512,13 +512,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MAT-001</t>
+          <t>MAT-010</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Step 1 needs MAT-010</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -531,7 +535,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SKU-A10</t>
+          <t>SKU-E10</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -539,7 +543,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PACK-STD</t>
+          <t>PACK-NEW</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -553,11 +557,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FINAL</t>
+          <t>Final step</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -568,7 +572,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SKU-A30</t>
+          <t>SKU-E30</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -576,7 +580,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FILL-STD</t>
+          <t>FILL-NEW</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -586,7 +590,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MAT-001</t>
+          <t>MAT-011</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -605,7 +609,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKU-A30</t>
+          <t>SKU-E30</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -613,19 +617,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SEAL-AUTO</t>
+          <t>PACK-NEW</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TYPE-C</t>
+          <t>TYPE-B</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -638,20 +646,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKU-A30</t>
+          <t>SKU-F05</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PACK-STD</t>
+          <t>FILL-NEW</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TYPE-B</t>
+          <t>TYPE-A</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -660,7 +668,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FINAL</t>
+          <t>Single step</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -670,12 +678,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SKU-B04</t>
+          <t>MAT-010</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -683,12 +691,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PACK-STD</t>
+          <t>SEMI-MIX</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TYPE-B</t>
+          <t>TYPE-A</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -697,7 +705,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FINAL</t>
+          <t>Material final</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -707,12 +715,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SKU-B25</t>
+          <t>MAT-011</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -720,7 +728,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FILL-STD</t>
+          <t>SEMI-MIX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -728,375 +736,38 @@
           <t>TYPE-A</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>MAT-002</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Material final</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SKU-B25</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PACK-BULK</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>TYPE-B</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>FINAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SKU-C30</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>FILL-HI</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TYPE-A</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>MAT-003</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SKU-C30</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SEAL-AUTO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TYPE-C</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>0</v>
+          <t># EntityType: SKU or MATERIAL</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SKU-C30</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>PACK-STD</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TYPE-B</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>FINAL</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SKU-D01</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SEAL-AUTO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TYPE-C</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="n">
-        <v>0</v>
+          <t># IsFinalSeq: 1=final MRP trigger, 0=intermediate</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SKU-D01</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LABEL-AUTO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TYPE-C</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>FINAL</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MATERIAL</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MAT-001</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SEMI-PROC</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TYPE-D</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>FINAL</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MATERIAL</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MAT-002</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>SEMI-PROC</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TYPE-D</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MATERIAL</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MAT-002</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>SEMI-MIX</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TYPE-D</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>FINAL</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MATERIAL</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>MAT-003</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>SEMI-MIX</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TYPE-D</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>FINAL</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
+          <t># MinGapShifts: 0=adjacent OK, 1=1 shift gap, 2=2 shifts gap</t>
+        </is>
       </c>
     </row>
   </sheetData>
